--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786053446</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>8.092664</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,110 +635,214 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.06637</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786068821</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>12.066394</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786053446</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>8.092664</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,110 +739,214 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,110 +843,534 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,92 +843,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>13.42578</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.0762</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>L19453184</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,31 +947,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>13.42578</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.0762</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786072637</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>176.075803</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1070,17 +1070,17 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.06637</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786068821</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>12.066394</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786053446</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>8.092664</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,110 +1267,214 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,23 +763,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -786,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -890,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -920,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,92 +979,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>16.47999</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.6763</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>13.42578</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.0762</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>L19453184</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1083,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1174,7 +1198,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1240,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1250,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1314,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,110 +1395,534 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,39 +546,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,19 +651,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -671,26 +667,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,19 +755,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -783,26 +771,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -840,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,12 +866,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -952,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,31 +963,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1026,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1075,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1195,23 +1195,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1299,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1338,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,62 +1411,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,28 +1515,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1554,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1622,7 +1630,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1688,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1723,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1762,7 +1770,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,110 +1827,534 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,12 +766,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -794,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,19 +867,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -879,26 +883,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,7 +1075,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1411,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1458,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,28 +1523,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,28 +1627,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1666,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1770,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1800,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1810,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1827,62 +1835,54 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,31 +1939,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>13.42578</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.0762</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1986,7 +1994,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2016,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786072637</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>176.075803</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2051,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2054,17 +2062,17 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.06637</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2090,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2120,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786068821</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>12.066394</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,28 +2155,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786053446</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>8.092664</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,110 +2259,214 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,39 +546,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,54 +963,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1018,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,54 +1067,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1130,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,54 +1171,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1242,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,54 +1275,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1354,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,54 +1379,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1466,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1496,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1506,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,23 +1483,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1547,7 +1511,11 @@
           <t>Under/Over (4)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1600,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,31 +1595,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1674,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,31 +1707,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1778,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,28 +1819,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1882,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,27 +1923,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1967,34 +1947,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2059,23 +2035,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2098,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2139,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,23 +2147,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2202,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,23 +2251,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2283,7 +2279,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,110 +2363,1174 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>80.26999</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>100.49451</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>92.22997</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>115.467881</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16.47999</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.6763</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786084723</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>24.369671</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786079889</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>30.802721</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>107.13792</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786078469</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>330.927938</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786075639</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2.531343</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +643,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -906,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,31 +971,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1010,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1114,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,12 +1206,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1248,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,12 +1310,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,12 +1414,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1456,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,39 +1507,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1538,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,54 +1611,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -1650,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,39 +1715,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1819,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1931,23 +1931,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1970,7 +1978,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,12 +2050,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2112,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,12 +2147,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2154,39 +2162,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2259,19 +2267,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2279,26 +2283,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2371,19 +2371,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2391,26 +2387,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -2448,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2467,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2490,12 +2482,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2560,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,31 +2579,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,31 +2691,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2738,7 +2746,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2768,7 +2776,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2778,7 +2786,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2795,7 +2803,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2803,23 +2811,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2842,7 +2858,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,31 +2915,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2946,7 +2970,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,62 +3027,54 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3088,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3098,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3115,28 +3131,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3162,7 +3178,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3192,7 +3208,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3202,7 +3218,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3219,7 +3235,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3230,7 +3246,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3296,7 +3312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3306,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3323,28 +3339,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3370,7 +3386,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3400,7 +3416,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3410,7 +3426,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,110 +3443,534 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,27 +739,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,11 +763,7 @@
           <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +843,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +858,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,39 +955,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1026,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1059,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1138,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,28 +1171,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1242,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1275,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1346,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,28 +1387,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1450,7 +1434,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,28 +1491,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1554,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,31 +1595,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1658,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,31 +1707,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,31 +1819,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1866,7 +1874,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,12 +1931,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1938,22 +1946,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1978,7 +1986,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,12 +2043,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2050,12 +2058,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2120,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,12 +2155,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2162,22 +2170,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2267,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,15 +2275,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2283,7 +2295,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2306,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,23 +2379,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2387,7 +2407,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2440,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,12 +2491,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2482,12 +2506,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2552,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,12 +2603,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2594,12 +2618,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2664,7 +2688,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2674,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2691,12 +2715,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2706,12 +2730,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2776,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2786,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2803,7 +2827,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2818,12 +2842,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2888,7 +2912,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2922,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,7 +2939,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2930,12 +2954,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3000,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,31 +3051,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3074,7 +3106,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3104,7 +3136,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3146,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,31 +3163,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3178,7 +3218,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3248,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3258,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,7 +3275,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3243,23 +3283,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3282,7 +3330,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3312,7 +3360,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3322,7 +3370,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3339,31 +3387,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3386,7 +3442,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3416,7 +3472,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3426,7 +3482,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3443,12 +3499,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3458,47 +3514,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3528,7 +3584,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3538,7 +3594,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3555,31 +3611,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3602,7 +3666,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3632,7 +3696,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3642,7 +3706,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3659,31 +3723,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3706,7 +3778,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3736,7 +3808,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3746,7 +3818,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3763,23 +3835,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3787,7 +3863,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3840,7 +3920,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3850,7 +3930,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3867,110 +3947,5942 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>344.26996</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.8113</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786127649</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>424.36975</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4.99996</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.815</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786127314</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>6.13492</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>36.55</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.5012</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786127301</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>72.917706</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>55.59996</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.8125</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786127301</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>68.43072</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>13.94</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.4988</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786126541</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>27.949875</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>15.30389</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.4925</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786126463</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>31.073888</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>17.9835</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.3575</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786126462</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>50.303497</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>17.37973</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786126462</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>28.259724</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.6138</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786126324</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2.704684</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>13.42</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.5063</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786126323</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>26.508642</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.1987</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19457072</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786126259</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786293000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>20.477987</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>RSC Anderlecht</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19457072</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786126255</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786293000</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>21.282609</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>24.75</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.6125</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786126126</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>40.408163</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786125835</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>10.230179</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2.24657</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786125800</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>4.596563</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21.49</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.0737</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786125572</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>291.389831</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>80.45</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.5225</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786124871</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>153.971292</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>99.99999</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.5225</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786124841</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>191.387541</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>15.29</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.0725</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786123773</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>210.896552</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>64.92966</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.8788</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786123019</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>73.88866</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14.21</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786122377</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>27.326923</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>53.28297</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786122377</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>102.46725</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786122212</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.1325</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786121396</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>30.188679</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>17.97999</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.875</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786120528</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>20.54856</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>5.21</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.3862</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786120011</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>13.488673</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>4.61</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.3862</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786119466</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>11.935275</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>7.08</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.3862</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786116893</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>18.330097</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.505</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786116378</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>297.029703</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>40.57051</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786115848</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>135.235033</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.2937</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786115833</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>34.042553</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.2937</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786115818</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>40.851064</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>9.52632</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.2963</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786115807</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>32.156354</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.7069</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.295</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786115795</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>5.786102</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>12.16858</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.295</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786115779</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>41.249424</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>16.20886</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.295</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786115758</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>54.945288</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>9.54904</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786115106</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>25.129053</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>116.54545</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.8013</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786112573</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>145.45454</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>14.27</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786111169</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>28.755668</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>16.44995</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.8712</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786107764</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>18.880861</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>15.56556</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.2087</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786106877</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>74.565557</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>39.38</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786102693</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>49.37931</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>164.62998</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786099074</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>206.109521</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>58.71998</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786098454</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>73.514842</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>80.26999</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>100.49451</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>92.22997</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>115.467881</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>16.47999</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.6763</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786084723</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>24.369671</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786079889</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>30.802721</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>107.13792</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786078469</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>330.927938</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786075639</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>2.531343</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V87"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
+          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>269.96</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.0588</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786129260</t>
+          <t>1786133616</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>474.654945</t>
+          <t>365.617021</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,31 +643,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
+          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.53431</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -682,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786128818</t>
+          <t>1786129775</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>106.094314</t>
+          <t>146.452555</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +755,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>122.26618</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786128755</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>201.676173</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786128752</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>489.6</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,17 +974,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>222.324</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7325</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786128730</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>303.513993</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,12 +1067,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1074,12 +1082,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>28.31998</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1089,7 +1097,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1114,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786128484</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34.536561</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,28 +1179,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786128396</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.941748</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1290,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1330,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786128227</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>49.029046</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1398,17 +1406,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>134.05326</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1434,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786128166</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>152.33325</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1499,23 +1507,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1538,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786128067</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>15.902041</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,27 +1611,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>308.60024</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1623,11 +1635,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1650,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1680,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786128055</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>379.81568</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,39 +1715,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>79.10999</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786128051</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>97.366142</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,12 +1819,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786128045</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,12 +1931,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786128044</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128042</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2155,7 +2155,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128041</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2267,12 +2267,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.23999</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128039</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3.98768</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,12 +2379,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128018</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>31.458462</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.28997</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128016</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>58.20304</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>98.03998</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128011</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>120.664591</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33.29998</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128009</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>40.984591</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,12 +2827,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1631.86998</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786127865</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2008.45536</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,12 +2939,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786127791</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>434.449231</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,12 +3051,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2495.72998</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786127694</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3076.400592</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,7 +3163,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>684.26</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786127681</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>843.46379</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,12 +3275,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>133.37999</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786127674</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>164.412931</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>581.61996</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786127673</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>716.94294</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3499,12 +3499,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3514,22 +3514,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2.30963</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127672</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>5.922128</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,12 +3611,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786127659</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3723,12 +3723,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3738,22 +3738,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786127658</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3835,12 +3835,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>48.74996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786127651</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>60.092401</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3947,12 +3947,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>344.26996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786127649</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>424.36975</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4059,12 +4059,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.99996</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127314</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.13492</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4186,22 +4186,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>344.26996</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127649</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>72.917706</t>
+          <t>424.36975</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>55.59996</t>
+          <t>4.99996</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127314</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>68.43072</t>
+          <t>6.13492</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786126541</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>27.949875</t>
+          <t>72.917706</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4507,7 +4507,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4515,23 +4515,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.30389</t>
+          <t>55.59996</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -4554,7 +4562,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4584,7 +4592,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786126463</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>31.073888</t>
+          <t>68.43072</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4611,7 +4619,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4619,23 +4627,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.9835</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3575</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -4658,7 +4674,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4688,7 +4704,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786126541</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4698,7 +4714,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>50.303497</t>
+          <t>27.949875</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4715,7 +4731,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4726,17 +4742,17 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>17.37973</t>
+          <t>15.30389</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4762,7 +4778,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4792,7 +4808,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786126463</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4802,7 +4818,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>28.259724</t>
+          <t>31.073888</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4819,28 +4835,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>17.9835</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.3575</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4866,7 +4882,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4896,7 +4912,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786126324</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4922,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2.704684</t>
+          <t>50.303497</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,28 +4939,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>17.37973</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4970,7 +4986,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5000,7 +5016,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786126323</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5010,7 +5026,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>26.508642</t>
+          <t>28.259724</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5027,39 +5043,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>RAAL La Louviere</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5067,27 +5075,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -5112,17 +5120,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786126259</t>
+          <t>1786126324</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>20.477987</t>
+          <t>2.704684</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5139,28 +5147,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5171,27 +5179,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5216,17 +5224,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786126255</t>
+          <t>1786126323</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>21.282609</t>
+          <t>26.508642</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5243,31 +5251,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5275,27 +5291,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5320,17 +5336,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786126126</t>
+          <t>1786126259</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>40.408163</t>
+          <t>20.477987</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5347,28 +5363,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5379,27 +5395,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5424,17 +5440,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786125835</t>
+          <t>1786126255</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10.230179</t>
+          <t>21.282609</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5451,28 +5467,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2.24657</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5498,7 +5514,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5528,7 +5544,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786125800</t>
+          <t>1786126126</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5538,7 +5554,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>4.596563</t>
+          <t>40.408163</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5555,62 +5571,54 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5640,7 +5648,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786125572</t>
+          <t>1786125835</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5650,7 +5658,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>291.389831</t>
+          <t>10.230179</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5667,27 +5675,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>2.24657</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5695,11 +5699,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786124871</t>
+          <t>1786125800</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>153.971292</t>
+          <t>4.596563</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5779,12 +5779,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5794,22 +5794,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>99.99999</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786124841</t>
+          <t>1786125572</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>191.387541</t>
+          <t>291.389831</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,12 +5891,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5906,47 +5906,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786123773</t>
+          <t>1786124871</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>210.896552</t>
+          <t>153.971292</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6003,31 +6003,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>64.92966</t>
+          <t>99.99999</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6050,7 +6058,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6080,7 +6088,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786123019</t>
+          <t>1786124841</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6090,7 +6098,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>73.88866</t>
+          <t>191.387541</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,12 +6115,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6122,22 +6130,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6162,7 +6170,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6192,7 +6200,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786123773</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6202,7 +6210,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>27.326923</t>
+          <t>210.896552</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,7 +6227,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6227,31 +6235,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>53.28297</t>
+          <t>64.92966</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786123019</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>102.46725</t>
+          <t>73.88866</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6346,22 +6346,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786122212</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>27.326923</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6443,12 +6443,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6458,22 +6458,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>53.28297</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>102.46725</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6555,7 +6555,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6563,23 +6563,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6602,7 +6610,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786122212</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6642,7 +6650,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6659,12 +6667,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6674,22 +6682,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6714,7 +6722,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6744,7 +6752,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6754,7 +6762,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6771,7 +6779,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6779,31 +6787,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,7 +6883,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,12 +6995,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7010,22 +7010,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV -2.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7107,31 +7107,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7154,7 +7162,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7184,7 +7192,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7194,7 +7202,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7211,31 +7219,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7258,7 +7274,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7288,7 +7304,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7298,7 +7314,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7315,7 +7331,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7326,12 +7342,12 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7392,7 +7408,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7402,7 +7418,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7419,7 +7435,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7430,12 +7446,12 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7496,7 +7512,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7506,7 +7522,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7523,7 +7539,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7534,12 +7550,12 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7600,7 +7616,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7610,7 +7626,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7627,7 +7643,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7638,12 +7654,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7704,7 +7720,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7714,7 +7730,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7731,7 +7747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7742,7 +7758,7 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7808,7 +7824,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7818,7 +7834,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7835,39 +7851,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7890,7 +7898,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7920,7 +7928,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7930,7 +7938,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7947,39 +7955,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8059,12 +8059,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8074,22 +8074,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8171,23 +8171,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8195,7 +8199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8218,7 +8226,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8248,7 +8256,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8258,7 +8266,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8275,31 +8283,39 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8322,7 +8338,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8352,7 +8368,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8362,7 +8378,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8379,7 +8395,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8387,19 +8403,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8407,11 +8419,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8434,7 +8442,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8464,7 +8472,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8474,7 +8482,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8491,7 +8499,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8499,19 +8507,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8519,11 +8523,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8603,7 +8603,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8715,7 +8715,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8827,7 +8827,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8939,31 +8939,39 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8986,7 +8994,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9016,7 +9024,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9026,7 +9034,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9043,31 +9051,39 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9090,7 +9106,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9120,7 +9136,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9130,7 +9146,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9147,28 +9163,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9194,7 +9210,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9224,7 +9240,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9234,7 +9250,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9251,28 +9267,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9298,7 +9314,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9328,7 +9344,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9338,7 +9354,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9355,62 +9371,54 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9440,7 +9448,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9450,7 +9458,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9467,28 +9475,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9514,7 +9522,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9544,7 +9552,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9554,7 +9562,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9571,31 +9579,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>13.42578</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.0762</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9618,7 +9634,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9648,7 +9664,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786072637</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9658,7 +9674,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>176.075803</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9675,28 +9691,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.06637</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9722,7 +9738,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9752,7 +9768,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786068821</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9762,7 +9778,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>12.066394</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9779,110 +9795,318 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T89" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="U89" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="V89" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
+          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>1.00993</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0588</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786133616</t>
+          <t>1786138046</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>365.617021</t>
+          <t>1.14928</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
+          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.0588</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786129775</t>
+          <t>1786133616</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>146.452555</t>
+          <t>365.617021</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
+          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,23 +755,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>269.96</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -802,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786129260</t>
+          <t>1786129775</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>474.654945</t>
+          <t>146.452555</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24.53431</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786128818</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>106.094314</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,17 +974,17 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>122.26618</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786128755</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>201.676173</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1122,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786128752</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>489.6</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1171,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>222.324</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7325</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786128730</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>303.513993</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,39 +1283,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>28.31998</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1338,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786128484</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>34.536561</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,23 +1395,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786128396</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.941748</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1507,31 +1507,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1554,7 +1546,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786128227</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>49.029046</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1619,23 +1611,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>134.05326</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>Under/Over (4.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786128166</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>152.33325</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1726,17 +1726,17 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786128067</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>15.902041</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,39 +1819,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>308.60024</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1874,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1904,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786128055</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>379.81568</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1931,12 +1923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>79.10999</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2016,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786128051</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>97.366142</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2058,7 +2050,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2128,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128045</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2240,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128044</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2267,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2352,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128042</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2379,7 +2371,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2464,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128041</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2491,12 +2483,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2506,7 +2498,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.23999</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2576,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128039</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2586,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.98768</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,12 +2595,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2618,7 +2610,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2688,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128018</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2698,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>31.458462</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2715,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.28997</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2800,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128016</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>58.20304</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,7 +2819,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2842,7 +2834,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>98.03998</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2912,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128011</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>120.664591</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,7 +2931,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2954,7 +2946,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>33.29998</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3024,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128009</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3034,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>40.984591</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3051,12 +3043,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3066,7 +3058,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1631.86998</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3136,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786127865</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3146,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2008.45536</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3163,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3178,7 +3170,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3248,7 +3240,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786127791</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3258,7 +3250,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>434.449231</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3275,12 +3267,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3290,12 +3282,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2495.72998</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3360,7 +3352,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786127694</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3370,7 +3362,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3076.400592</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3387,12 +3379,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3402,7 +3394,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>684.26</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3472,7 +3464,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786127681</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3482,7 +3474,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>843.46379</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3499,7 +3491,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3514,7 +3506,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>133.37999</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3584,7 +3576,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127674</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3594,7 +3586,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>164.412931</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3611,7 +3603,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3626,7 +3618,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>581.61996</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3696,7 +3688,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786127673</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3706,7 +3698,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>716.94294</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3723,12 +3715,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3738,22 +3730,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2.30963</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3778,7 +3770,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3808,7 +3800,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786127672</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3818,7 +3810,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>5.922128</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3835,12 +3827,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3850,22 +3842,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3890,7 +3882,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3920,7 +3912,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786127659</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3930,7 +3922,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3947,7 +3939,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4032,7 +4024,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786127658</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4059,12 +4051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4074,7 +4066,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>48.74996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4144,7 +4136,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127651</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4154,7 +4146,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>60.092401</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4171,7 +4163,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4186,7 +4178,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>344.26996</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4256,7 +4248,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127649</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4266,7 +4258,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>424.36975</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4283,12 +4275,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4298,12 +4290,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.99996</t>
+          <t>344.26996</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4368,7 +4360,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127314</t>
+          <t>1786127649</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4378,7 +4370,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.13492</t>
+          <t>424.36975</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4395,12 +4387,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4410,22 +4402,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>4.99996</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4450,7 +4442,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4480,7 +4472,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127314</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4490,7 +4482,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>72.917706</t>
+          <t>6.13492</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4507,7 +4499,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4522,22 +4514,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>55.59996</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4562,7 +4554,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4602,7 +4594,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>68.43072</t>
+          <t>72.917706</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4619,7 +4611,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4634,22 +4626,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>55.59996</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4674,7 +4666,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4704,7 +4696,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786126541</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4714,7 +4706,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>27.949875</t>
+          <t>68.43072</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4731,7 +4723,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4739,23 +4731,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.30389</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786126463</t>
+          <t>1786126541</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>31.073888</t>
+          <t>27.949875</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4835,7 +4835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4846,17 +4846,17 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.9835</t>
+          <t>15.30389</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3575</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786126463</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>50.303497</t>
+          <t>31.073888</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4950,17 +4950,17 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.37973</t>
+          <t>17.9835</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.3575</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>28.259724</t>
+          <t>50.303497</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5043,28 +5043,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>17.37973</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786126324</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.704684</t>
+          <t>28.259724</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5158,17 +5158,17 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786126323</t>
+          <t>1786126324</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>26.508642</t>
+          <t>2.704684</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5251,39 +5251,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>RAAL La Louviere</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5291,27 +5283,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5336,17 +5328,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786126259</t>
+          <t>1786126323</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>20.477987</t>
+          <t>26.508642</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5363,7 +5355,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5371,15 +5363,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5387,7 +5383,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786126255</t>
+          <t>1786126259</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>21.282609</t>
+          <t>20.477987</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5467,28 +5467,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5499,27 +5499,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5544,17 +5544,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786126126</t>
+          <t>1786126255</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>40.408163</t>
+          <t>21.282609</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,28 +5571,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786125835</t>
+          <t>1786126126</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10.230179</t>
+          <t>40.408163</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5675,18 +5675,18 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2.24657</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786125800</t>
+          <t>1786125835</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>4.596563</t>
+          <t>10.230179</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5779,62 +5779,54 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>2.24657</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5864,7 +5856,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786125572</t>
+          <t>1786125800</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5874,7 +5866,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>291.389831</t>
+          <t>4.596563</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5891,12 +5883,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5906,22 +5898,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5946,7 +5938,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5976,7 +5968,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786124871</t>
+          <t>1786125572</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5986,7 +5978,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>153.971292</t>
+          <t>291.389831</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6003,7 +5995,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6018,7 +6010,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>99.99999</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6088,7 +6080,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786124841</t>
+          <t>1786124871</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6098,7 +6090,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>191.387541</t>
+          <t>153.971292</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6115,12 +6107,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6130,47 +6122,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>99.99999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6200,7 +6192,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786123773</t>
+          <t>1786124841</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6210,7 +6202,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>210.896552</t>
+          <t>191.387541</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6227,23 +6219,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>64.92966</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6251,7 +6247,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786123019</t>
+          <t>1786123773</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>73.88866</t>
+          <t>210.896552</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6339,31 +6339,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>64.92966</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6386,7 +6378,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6416,7 +6408,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786123019</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6426,7 +6418,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>27.326923</t>
+          <t>73.88866</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6443,7 +6435,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6458,7 +6450,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>53.28297</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6538,7 +6530,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>102.46725</t>
+          <t>27.326923</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6555,7 +6547,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6570,22 +6562,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>53.28297</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6610,7 +6602,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6640,7 +6632,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786122212</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6650,7 +6642,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>102.46725</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6667,12 +6659,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6682,22 +6674,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6722,7 +6714,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6752,7 +6744,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786122212</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6762,7 +6754,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6779,23 +6771,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6803,7 +6799,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,7 +6883,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6891,31 +6891,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6938,7 +6930,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6968,7 +6960,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +6970,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,7 +6987,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7010,7 +7002,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7080,7 +7072,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7090,7 +7082,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7107,7 +7099,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7122,7 +7114,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7192,7 +7184,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7202,7 +7194,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7219,12 +7211,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -7234,22 +7226,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV -2.5</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7274,7 +7266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7304,7 +7296,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7314,7 +7306,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7331,31 +7323,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7446,12 +7446,12 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7550,7 +7550,7 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7643,7 +7643,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7654,12 +7654,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7758,12 +7758,12 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7862,7 +7862,7 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7955,7 +7955,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7966,7 +7966,7 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8059,39 +8059,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8114,7 +8106,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8144,7 +8136,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8154,7 +8146,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8171,12 +8163,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8186,22 +8178,22 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8226,7 +8218,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8256,7 +8248,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8266,7 +8258,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8283,12 +8275,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8298,22 +8290,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8338,7 +8330,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8368,7 +8360,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8378,7 +8370,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8395,31 +8387,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8499,7 +8499,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8510,12 +8510,12 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8603,7 +8603,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8611,19 +8611,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8631,11 +8627,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8688,7 +8680,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8698,7 +8690,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8715,7 +8707,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8730,12 +8722,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8800,7 +8792,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8810,7 +8802,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8827,7 +8819,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8842,7 +8834,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8912,7 +8904,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8922,7 +8914,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8939,7 +8931,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8954,7 +8946,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -9024,7 +9016,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9034,7 +9026,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9051,7 +9043,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9066,7 +9058,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9146,7 +9138,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9163,31 +9155,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9267,28 +9267,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9371,28 +9371,28 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9475,28 +9475,28 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9579,62 +9579,54 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9664,7 +9656,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9674,7 +9666,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9691,31 +9683,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>13.42578</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.0762</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786072637</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>176.075803</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9795,7 +9795,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9806,17 +9806,17 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.06637</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786068821</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>12.066394</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9899,28 +9899,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786053446</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>8.092664</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10003,110 +10003,214 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="T90" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="U90" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="V90" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
+          <t>0x3682c29acf60c0dd6b7204b9540a6266714a3c2ac807800fcfbefee955954bcb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00993</t>
+          <t>29.38999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786138046</t>
+          <t>1786179429</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.14928</t>
+          <t>56.114539</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
+          <t>0x00da5541f47274f81a987850455ebf6974f1794b7c0c6de63de3bf7812b4b198</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.0588</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>KVC Westerlo vs R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x446634efd727b2ef8bf251a191d1a7adf03939ea15fc66483ea568f8490e8d26</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453183</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786133616</t>
+          <t>1786176782</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>365.617021</t>
+          <t>136.339286</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
+          <t>0x811eb7da21a4f297ed99b71c62d942341bcfb84e4030c6a1b2583e59d5b38248</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>29.51999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Saint-Truiden VV -1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786129775</t>
+          <t>1786176744</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>146.452555</t>
+          <t>56.362749</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
+          <t>0x9beed733469e724bd6c204e6d1758b8f78df08603ec5dcb7f1345f5b7855f05b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>269.96</t>
+          <t>107.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.6438</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -891,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x0e8a6aba98b8efbd7b13f11140ff85974fc8741094562833dce18f9958e3a56d</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786129260</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>474.654945</t>
+          <t>167.68932</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,23 +979,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
+          <t>0x866b09603f0681c7636d7decb90bc14a623d02cda27a0e847225f18eeac82ace</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.53431</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,7 +1007,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -995,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786128818</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>106.094314</t>
+          <t>43.570406</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,23 +1091,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
+          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>122.26618</t>
+          <t>1.00993</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1099,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786128755</t>
+          <t>1786138046</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>201.676173</t>
+          <t>1.14928</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
+          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.0588</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1226,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786128752</t>
+          <t>1786133616</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>489.6</t>
+          <t>365.617021</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,31 +1307,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
+          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>222.324</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7325</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1330,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786128730</t>
+          <t>1786129775</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>303.513993</t>
+          <t>146.452555</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,39 +1419,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.31998</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786128484</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>34.536561</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,28 +1523,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1546,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1576,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786128396</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.941748</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,39 +1627,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1658,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786128227</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>49.029046</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,23 +1731,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>134.05326</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1739,7 +1759,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1792,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786128166</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>152.33325</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1843,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1866,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786128067</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>15.902041</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,12 +1947,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1938,12 +1962,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>308.60024</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2008,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786128055</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>379.81568</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,39 +2059,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79.10999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2090,7 +2106,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2120,7 +2136,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128051</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2146,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>97.366142</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,12 +2163,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2162,22 +2178,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2202,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128045</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,27 +2275,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2287,11 +2299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2314,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2344,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128044</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,39 +2379,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128042</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,12 +2483,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128041</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.23999</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128039</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.98768</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128018</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>31.458462</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,12 +2819,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.28997</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128016</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>58.20304</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>98.03998</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128011</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>120.664591</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,12 +3043,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33.29998</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128009</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>40.984591</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3155,7 +3155,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1631.86998</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786127865</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2008.45536</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3267,12 +3267,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786127791</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>434.449231</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,12 +3379,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2495.72998</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786127694</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3076.400592</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,12 +3491,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>684.26</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786127681</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>843.46379</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3603,12 +3603,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>133.37999</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786127674</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>164.412931</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>581.61996</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786127673</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>716.94294</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3827,12 +3827,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3842,22 +3842,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.30963</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786127672</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>5.922128</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786127659</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4051,12 +4051,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127658</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4163,12 +4163,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>48.74996</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127651</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>60.092401</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4275,12 +4275,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>344.26996</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127649</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>424.36975</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4387,12 +4387,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4402,22 +4402,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4.99996</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786127314</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>6.13492</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4514,22 +4514,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>72.917706</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4611,12 +4611,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>55.59996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>68.43072</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4723,7 +4723,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786126541</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>27.949875</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4835,7 +4835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4843,23 +4843,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>15.30389</t>
+          <t>344.26996</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -4882,7 +4890,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4912,7 +4920,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786126463</t>
+          <t>1786127649</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4922,7 +4930,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>31.073888</t>
+          <t>424.36975</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4939,31 +4947,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.9835</t>
+          <t>4.99996</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3575</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -4986,7 +5002,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -5016,7 +5032,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786127314</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5026,7 +5042,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>50.303497</t>
+          <t>6.13492</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5043,7 +5059,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5051,23 +5067,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>17.37973</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5090,7 +5114,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5120,7 +5144,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5130,7 +5154,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>28.259724</t>
+          <t>72.917706</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5147,31 +5171,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>55.59996</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5194,7 +5226,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5224,7 +5256,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786126324</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5234,7 +5266,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>2.704684</t>
+          <t>68.43072</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5251,23 +5283,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5275,7 +5311,11 @@
           <t>Asian Handicap (-2)</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5328,7 +5368,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786126323</t>
+          <t>1786126541</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5338,7 +5378,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>26.508642</t>
+          <t>27.949875</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5355,39 +5395,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>15.30389</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>RAAL La Louviere</t>
-        </is>
-      </c>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5395,27 +5427,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5440,17 +5472,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786126259</t>
+          <t>1786126463</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>20.477987</t>
+          <t>31.073888</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5467,28 +5499,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>17.9835</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.3575</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5499,27 +5531,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5544,17 +5576,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786126255</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>21.282609</t>
+          <t>50.303497</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5571,28 +5603,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>17.37973</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5618,7 +5650,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5648,7 +5680,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786126126</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5658,7 +5690,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>40.408163</t>
+          <t>28.259724</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5675,28 +5707,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5722,7 +5754,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5752,7 +5784,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786125835</t>
+          <t>1786126324</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5762,7 +5794,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>10.230179</t>
+          <t>2.704684</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5779,28 +5811,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.24657</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5826,7 +5858,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5856,7 +5888,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786125800</t>
+          <t>1786126323</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5866,7 +5898,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4.596563</t>
+          <t>26.508642</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5883,12 +5915,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5898,12 +5930,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5913,7 +5945,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5923,27 +5955,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5968,17 +6000,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786125572</t>
+          <t>1786126259</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>291.389831</t>
+          <t>20.477987</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5995,39 +6027,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6035,27 +6059,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6080,17 +6104,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786124871</t>
+          <t>1786126255</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>153.971292</t>
+          <t>21.282609</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6107,39 +6131,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>99.99999</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6162,7 +6178,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6192,7 +6208,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786124841</t>
+          <t>1786126126</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6202,7 +6218,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>191.387541</t>
+          <t>40.408163</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6219,62 +6235,54 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6304,7 +6312,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786123773</t>
+          <t>1786125835</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6314,7 +6322,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>210.896552</t>
+          <t>10.230179</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6331,28 +6339,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>64.92966</t>
+          <t>2.24657</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6378,7 +6386,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6408,7 +6416,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786123019</t>
+          <t>1786125800</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6418,7 +6426,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>73.88866</t>
+          <t>4.596563</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6435,12 +6443,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6450,22 +6458,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6490,7 +6498,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6520,7 +6528,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786125572</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6530,7 +6538,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>27.326923</t>
+          <t>291.389831</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6547,12 +6555,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6562,12 +6570,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>53.28297</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6632,7 +6640,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786124871</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6642,7 +6650,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>102.46725</t>
+          <t>153.971292</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6659,12 +6667,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6674,22 +6682,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>99.99999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6714,7 +6722,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6744,7 +6752,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786122212</t>
+          <t>1786124841</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6754,7 +6762,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>191.387541</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6771,12 +6779,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6786,12 +6794,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6801,7 +6809,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6826,7 +6834,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6856,7 +6864,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786123773</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6874,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>210.896552</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,7 +6891,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6894,12 +6902,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>64.92966</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6960,7 +6968,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786123019</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6970,7 +6978,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>73.88866</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6987,7 +6995,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7002,22 +7010,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7042,7 +7050,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7072,7 +7080,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7082,7 +7090,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>27.326923</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7099,7 +7107,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7114,22 +7122,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>53.28297</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7154,7 +7162,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7184,7 +7192,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7194,7 +7202,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>102.46725</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7211,7 +7219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7226,22 +7234,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7266,7 +7274,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7296,7 +7304,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786122212</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7306,7 +7314,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7323,12 +7331,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7338,22 +7346,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7378,7 +7386,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7408,7 +7416,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7418,7 +7426,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7435,28 +7443,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7482,7 +7490,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7512,7 +7520,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7522,7 +7530,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7539,31 +7547,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7586,7 +7602,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7616,7 +7632,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7626,7 +7642,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7643,31 +7659,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7690,7 +7714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7720,7 +7744,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7730,7 +7754,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7747,31 +7771,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7794,7 +7826,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7824,7 +7856,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7834,7 +7866,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7851,31 +7883,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7898,7 +7938,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7928,7 +7968,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7938,7 +7978,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7955,7 +7995,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7966,12 +8006,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8032,7 +8072,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8042,7 +8082,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8059,7 +8099,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8070,12 +8110,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8136,7 +8176,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8146,7 +8186,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8163,39 +8203,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8218,7 +8250,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8248,7 +8280,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8258,7 +8290,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8275,39 +8307,31 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8330,7 +8354,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8360,7 +8384,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8370,7 +8394,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8387,39 +8411,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8442,7 +8458,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8472,7 +8488,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8482,7 +8498,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8499,28 +8515,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8546,7 +8562,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8576,7 +8592,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8586,7 +8602,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8603,28 +8619,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8650,7 +8666,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8680,7 +8696,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8690,7 +8706,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8707,7 +8723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8722,22 +8738,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8762,7 +8778,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8792,7 +8808,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8802,7 +8818,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8819,12 +8835,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8834,12 +8850,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8904,7 +8920,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8914,7 +8930,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8931,12 +8947,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8946,22 +8962,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8986,7 +9002,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9016,7 +9032,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9026,7 +9042,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9043,7 +9059,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9051,19 +9067,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -9071,11 +9083,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9098,7 +9106,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9128,7 +9136,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9138,7 +9146,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9155,7 +9163,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9163,19 +9171,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9183,11 +9187,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9267,31 +9267,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9314,7 +9322,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9344,7 +9352,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9354,7 +9362,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9371,31 +9379,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9418,7 +9434,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9448,7 +9464,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9458,7 +9474,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9475,7 +9491,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9483,23 +9499,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9522,7 +9546,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9552,7 +9576,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9562,7 +9586,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9579,31 +9603,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9626,7 +9658,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9656,7 +9688,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9666,7 +9698,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9683,12 +9715,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9698,12 +9730,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9713,32 +9745,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9768,7 +9800,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9778,7 +9810,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9795,28 +9827,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9842,7 +9874,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9872,7 +9904,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9882,7 +9914,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9899,28 +9931,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -9946,7 +9978,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9976,7 +10008,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9986,7 +10018,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10003,28 +10035,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -10050,7 +10082,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10080,7 +10112,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10090,7 +10122,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10107,110 +10139,638 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786075639</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2.531343</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="T95" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="U95" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="V95" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3682c29acf60c0dd6b7204b9540a6266714a3c2ac807800fcfbefee955954bcb</t>
+          <t>0x98b046718238b1fcd44c4da6528214adbbf94cec7085be83998a597cd95b8e42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.38999</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Saint-Truiden VV -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Royal Antwerp FC vs Waasland-Beveren</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x2e62b0f92e344d08a9881b897546df0f5cec438d6ca14eb4a57ed9c49a70ab5a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19457069</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786179429</t>
+          <t>1786185126</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786295700</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>56.114539</t>
+          <t>18.941799</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x00da5541f47274f81a987850455ebf6974f1794b7c0c6de63de3bf7812b4b198</t>
+          <t>0xbf4973ce0a06b2d9d47e780f622a4b8196461d660d202ffe65bf9bc72f90bdf9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>R.Union Saint-Gilloise</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KVC Westerlo vs R.Union Saint-Gilloise</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>R.Union Saint-Gilloise</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x446634efd727b2ef8bf251a191d1a7adf03939ea15fc66483ea568f8490e8d26</t>
+          <t>0xd5800bf6a48bcd5b9e43eb6948ccabf7f9e554beb82e412a5fbb5da4ad572555</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19453183</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786176782</t>
+          <t>1786184656</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>136.339286</t>
+          <t>14.134276</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x811eb7da21a4f297ed99b71c62d942341bcfb84e4030c6a1b2583e59d5b38248</t>
+          <t>0x936a18fe1afdd087978f7d5e8f90ef2718bdecbfc78b8cdfa11764df4b942fd5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +762,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.51999</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV -1</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786176744</t>
+          <t>1786181026</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>56.362749</t>
+          <t>74.977346</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9beed733469e724bd6c204e6d1758b8f78df08603ec5dcb7f1345f5b7855f05b</t>
+          <t>0x3682c29acf60c0dd6b7204b9540a6266714a3c2ac807800fcfbefee955954bcb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -882,39 +874,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>107.95</t>
+          <t>29.38999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6438</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Saint-Truiden VV -1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV vs Lommel United</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Saint-Truiden VV</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Saint-Truiden VV</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Lommel United</t>
@@ -922,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x0e8a6aba98b8efbd7b13f11140ff85974fc8741094562833dce18f9958e3a56d</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786176743</t>
+          <t>1786179429</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>167.68932</t>
+          <t>56.114539</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x866b09603f0681c7636d7decb90bc14a623d02cda27a0e847225f18eeac82ace</t>
+          <t>0x00da5541f47274f81a987850455ebf6974f1794b7c0c6de63de3bf7812b4b198</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -994,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV -1</t>
+          <t>R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>KVC Westerlo vs R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x446634efd727b2ef8bf251a191d1a7adf03939ea15fc66483ea568f8490e8d26</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453183</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786176743</t>
+          <t>1786176782</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>43.570406</t>
+          <t>136.339286</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
+          <t>0x811eb7da21a4f297ed99b71c62d942341bcfb84e4030c6a1b2583e59d5b38248</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00993</t>
+          <t>29.51999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786138046</t>
+          <t>1786176744</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.14928</t>
+          <t>56.362749</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
+          <t>0x9beed733469e724bd6c204e6d1758b8f78df08603ec5dcb7f1345f5b7855f05b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>107.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.0588</t>
+          <t>1.6438</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x0e8a6aba98b8efbd7b13f11140ff85974fc8741094562833dce18f9958e3a56d</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786133616</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>365.617021</t>
+          <t>167.68932</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1307,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
+          <t>0x866b09603f0681c7636d7decb90bc14a623d02cda27a0e847225f18eeac82ace</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Saint-Truiden VV -1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786129775</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>146.452555</t>
+          <t>43.570406</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,28 +1419,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
+          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>269.96</t>
+          <t>1.00993</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1451,27 +1451,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786129260</t>
+          <t>1786138046</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>474.654945</t>
+          <t>1.14928</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
+          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1531,23 +1531,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.53431</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.0588</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1570,7 +1578,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786128818</t>
+          <t>1786133616</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>106.094314</t>
+          <t>365.617021</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,31 +1635,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
+          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>122.26618</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1674,7 +1690,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786128755</t>
+          <t>1786129775</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>201.676173</t>
+          <t>146.452555</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1747,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,31 +1755,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1786,7 +1794,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1816,7 +1824,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786128752</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1834,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>489.6</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,7 +1851,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1854,17 +1862,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>222.324</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7325</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1890,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786128730</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>303.513993</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,39 +1955,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28.31998</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786128484</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>34.536561</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,31 +2059,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2106,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2136,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128396</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2146,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.941748</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2163,39 +2171,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 4.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128227</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>49.029046</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2283,15 +2283,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>134.05326</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2299,7 +2303,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2322,7 +2330,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2352,7 +2360,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128166</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2370,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>152.33325</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,7 +2387,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2390,17 +2398,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2426,7 +2434,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2456,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128067</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2466,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>15.902041</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2483,12 +2491,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2498,22 +2506,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>308.60024</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2568,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128055</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>379.81568</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,27 +2603,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>79.10999</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2623,11 +2627,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128051</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>97.366142</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,39 +2707,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2762,7 +2754,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2792,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128045</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2802,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2819,12 +2811,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2834,7 +2826,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2904,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128044</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2914,7 +2906,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2931,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2946,7 +2938,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3016,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128042</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,7 +3035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3128,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128041</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3155,12 +3147,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3170,7 +3162,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.23999</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3240,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128039</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3250,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>3.98768</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3267,12 +3259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3282,7 +3274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3352,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786128018</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3362,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>31.458462</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3379,12 +3371,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3394,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.28997</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3464,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786128016</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3474,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>58.20304</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3491,12 +3483,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3506,7 +3498,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>98.03998</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3576,7 +3568,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786128011</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3586,7 +3578,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>120.664591</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3603,7 +3595,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3618,7 +3610,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>33.29998</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3688,7 +3680,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786128009</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3698,7 +3690,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>40.984591</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3715,12 +3707,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3730,7 +3722,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1631.86998</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3800,7 +3792,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786127865</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3810,7 +3802,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2008.45536</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3827,12 +3819,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3842,7 +3834,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3912,7 +3904,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786127791</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3922,7 +3914,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>434.449231</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3939,12 +3931,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3954,12 +3946,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2495.72998</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4024,7 +4016,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786127694</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4034,7 +4026,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3076.400592</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4051,7 +4043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4066,12 +4058,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>684.26</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4136,7 +4128,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127681</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4146,7 +4138,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>843.46379</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4163,7 +4155,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4178,12 +4170,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>133.37999</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4248,7 +4240,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127674</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4258,7 +4250,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>164.412931</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4275,12 +4267,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4290,7 +4282,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>581.61996</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4360,7 +4352,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127673</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4370,7 +4362,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>716.94294</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4387,12 +4379,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4402,22 +4394,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.30963</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4442,7 +4434,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4472,7 +4464,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786127672</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4482,7 +4474,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>5.922128</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4499,12 +4491,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4514,7 +4506,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4584,7 +4576,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786127659</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4594,7 +4586,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4611,12 +4603,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4626,7 +4618,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4696,7 +4688,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786127658</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4706,7 +4698,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4723,12 +4715,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4738,22 +4730,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>48.74996</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 4.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4778,7 +4770,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4808,7 +4800,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786127651</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4818,7 +4810,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>60.092401</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4835,12 +4827,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4850,7 +4842,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>344.26996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4920,7 +4912,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786127649</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4930,7 +4922,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>424.36975</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4947,7 +4939,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4962,12 +4954,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.99996</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5032,7 +5024,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786127314</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5042,7 +5034,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>6.13492</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5059,7 +5051,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5074,22 +5066,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5114,7 +5106,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5144,7 +5136,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5154,7 +5146,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>72.917706</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5171,7 +5163,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5186,12 +5178,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>55.59996</t>
+          <t>344.26996</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5256,7 +5248,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786127649</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>68.43072</t>
+          <t>424.36975</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5283,12 +5275,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5298,22 +5290,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>4.99996</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5338,7 +5330,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5368,7 +5360,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786126541</t>
+          <t>1786127314</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5378,7 +5370,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>27.949875</t>
+          <t>6.13492</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5395,7 +5387,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5403,23 +5395,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15.30389</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786126463</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>31.073888</t>
+          <t>72.917706</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5507,23 +5507,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.9835</t>
+          <t>55.59996</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3575</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5546,7 +5554,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5576,7 +5584,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5586,7 +5594,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>50.303497</t>
+          <t>68.43072</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5603,7 +5611,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5611,23 +5619,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>17.37973</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5650,7 +5666,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5680,7 +5696,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786126541</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5690,7 +5706,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>28.259724</t>
+          <t>27.949875</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5707,28 +5723,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>15.30389</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5754,7 +5770,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5784,7 +5800,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786126324</t>
+          <t>1786126463</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5794,7 +5810,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2.704684</t>
+          <t>31.073888</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5811,28 +5827,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>17.9835</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.3575</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5858,7 +5874,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5888,7 +5904,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786126323</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5898,7 +5914,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>26.508642</t>
+          <t>50.303497</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5915,39 +5931,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>17.37973</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>RAAL La Louviere</t>
-        </is>
-      </c>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5955,27 +5963,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6000,17 +6008,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786126259</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>20.477987</t>
+          <t>28.259724</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6027,28 +6035,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -6059,27 +6067,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6104,17 +6112,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786126255</t>
+          <t>1786126324</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>21.282609</t>
+          <t>2.704684</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6131,7 +6139,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6142,17 +6150,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -6178,7 +6186,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6208,7 +6216,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786126126</t>
+          <t>1786126323</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6218,7 +6226,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>40.408163</t>
+          <t>26.508642</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6235,31 +6243,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>RAAL La Louviere</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6267,27 +6283,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6312,17 +6328,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786125835</t>
+          <t>1786126259</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>10.230179</t>
+          <t>20.477987</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6339,28 +6355,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.24657</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -6371,27 +6387,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6416,17 +6432,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786125800</t>
+          <t>1786126255</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>4.596563</t>
+          <t>21.282609</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6443,62 +6459,54 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6528,7 +6536,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786125572</t>
+          <t>1786126126</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6538,7 +6546,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>291.389831</t>
+          <t>40.408163</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6555,27 +6563,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6583,11 +6587,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786124871</t>
+          <t>1786125835</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>153.971292</t>
+          <t>10.230179</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6667,27 +6667,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>99.99999</t>
+          <t>2.24657</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6695,11 +6691,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6752,7 +6744,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786124841</t>
+          <t>1786125800</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6762,7 +6754,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>191.387541</t>
+          <t>4.596563</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6779,7 +6771,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6794,12 +6786,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6864,7 +6856,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786123773</t>
+          <t>1786125572</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6874,7 +6866,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>210.896552</t>
+          <t>291.389831</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6891,31 +6883,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>64.92966</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786123019</t>
+          <t>1786124871</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>73.88866</t>
+          <t>153.971292</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,12 +6995,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>99.99999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786124841</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>27.326923</t>
+          <t>191.387541</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7107,12 +7107,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7122,22 +7122,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>53.28297</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786123773</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>102.46725</t>
+          <t>210.896552</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7219,7 +7219,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7227,31 +7227,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>64.92966</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7274,7 +7266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7304,7 +7296,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786122212</t>
+          <t>1786123019</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7314,7 +7306,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>73.88866</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7331,12 +7323,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7346,22 +7338,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7386,7 +7378,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7416,7 +7408,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7426,7 +7418,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>27.326923</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7443,7 +7435,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7451,23 +7443,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>53.28297</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>102.46725</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7547,7 +7547,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7562,22 +7562,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786122212</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7659,12 +7659,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -7674,22 +7674,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7771,7 +7771,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7779,31 +7779,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7826,7 +7818,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7856,7 +7848,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7866,7 +7858,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7883,12 +7875,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7898,22 +7890,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV -2.5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7938,7 +7930,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7968,7 +7960,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7978,7 +7970,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7995,31 +7987,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8099,31 +8099,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8146,7 +8154,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8176,7 +8184,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8186,7 +8194,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8203,31 +8211,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8250,7 +8266,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8280,7 +8296,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8290,7 +8306,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8307,7 +8323,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8318,12 +8334,12 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -8384,7 +8400,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8394,7 +8410,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8411,7 +8427,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8422,12 +8438,12 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8488,7 +8504,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8498,7 +8514,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8515,7 +8531,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8526,12 +8542,12 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8592,7 +8608,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8602,7 +8618,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8619,7 +8635,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8630,12 +8646,12 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8696,7 +8712,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8706,7 +8722,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8723,39 +8739,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8778,7 +8786,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8808,7 +8816,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8818,7 +8826,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8835,39 +8843,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8947,39 +8947,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9002,7 +8994,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9032,7 +9024,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9042,7 +9034,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9059,7 +9051,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9067,23 +9059,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9163,23 +9163,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -9187,7 +9191,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9240,7 +9248,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9250,7 +9258,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9267,12 +9275,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9282,22 +9290,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9322,7 +9330,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9352,7 +9360,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786111169</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9362,7 +9370,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>28.755668</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9379,7 +9387,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9387,19 +9395,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>16.44995</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8712</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9407,11 +9411,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786107764</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>18.880861</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9499,19 +9499,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>15.56556</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2087</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9519,11 +9515,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9576,7 +9568,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786106877</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9586,7 +9578,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>74.565557</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9603,7 +9595,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9618,12 +9610,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.7975</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9688,7 +9680,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786102693</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9698,7 +9690,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>49.37931</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9715,7 +9707,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9730,7 +9722,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>164.62998</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -9800,7 +9792,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786099074</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9810,7 +9802,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>206.109521</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9827,31 +9819,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>58.71998</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786098454</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>73.514842</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9931,31 +9931,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>80.26999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9978,7 +9986,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10008,7 +10016,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10018,7 +10026,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>100.49451</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10035,7 +10043,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10043,23 +10051,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>92.22997</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -10082,7 +10098,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10112,7 +10128,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786098453</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10122,7 +10138,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>115.467881</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10139,28 +10155,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>16.47999</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10186,7 +10202,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10216,7 +10232,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786084723</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10226,7 +10242,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>24.369671</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10243,62 +10259,54 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>16.98</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.5513</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10328,7 +10336,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786079889</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10338,7 +10346,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>30.802721</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10355,7 +10363,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10366,17 +10374,17 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>107.13792</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.3237</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10402,7 +10410,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10432,7 +10440,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786078469</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10442,7 +10450,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>330.927938</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10459,28 +10467,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -10506,7 +10514,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10536,7 +10544,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786075639</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10546,7 +10554,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>2.531343</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10563,7 +10571,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10571,15 +10579,19 @@
           <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>13.42578</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.0762</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10587,7 +10599,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -10610,7 +10626,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10640,7 +10656,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786072637</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10650,7 +10666,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>176.075803</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10667,110 +10683,422 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T98" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="U98" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="V98" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/Jupiler League/trades.xlsx
+++ b/data/sxbet/ligas/Jupiler League/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x98b046718238b1fcd44c4da6528214adbbf94cec7085be83998a597cd95b8e42</t>
+          <t>0xd300c03f52fab90a6c88b7181f93c4a7816b72220b5a693aa0a3b31f2ee34cdd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4725</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Standard de Liege</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC vs Waasland-Beveren</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x2e62b0f92e344d08a9881b897546df0f5cec438d6ca14eb4a57ed9c49a70ab5a</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19457069</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786185126</t>
+          <t>1786204870</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786295700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>18.941799</t>
+          <t>2.380952</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xbf4973ce0a06b2d9d47e780f622a4b8196461d660d202ffe65bf9bc72f90bdf9</t>
+          <t>0xc4a401b71b193bff0d4c7c9b0c035796e714e8fd353cdf98e5d7538f4c7fc1f1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>380.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3538</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Jupiler League</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Standard de Liege 0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd5800bf6a48bcd5b9e43eb6948ccabf7f9e554beb82e412a5fbb5da4ad572555</t>
+          <t>0x9328587a10f85b7926851709a75b7375b80be67ff4c9dbec51091d4e4551a6a5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786184656</t>
+          <t>1786204513</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>14.134276</t>
+          <t>674.554324</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x936a18fe1afdd087978f7d5e8f90ef2718bdecbfc78b8cdfa11764df4b942fd5</t>
+          <t>0xd22c2d9064b1bd368d629b8c1f2674f8d56700355325729661da401f6525bf96</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,39 +770,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>11.35856</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.2363</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Standard de Liege -1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Standard de Liege</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Standard de Liege vs Cercle Brugge KSV</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Standard de Liege</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Cercle Brugge KSV</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
+          <t>0x2c46ab9584be52cc20f20a264840dedcce2808026a884c7d27070dd3aab052b4</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786181026</t>
+          <t>1786204512</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>74.977346</t>
+          <t>48.078561</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x3682c29acf60c0dd6b7204b9540a6266714a3c2ac807800fcfbefee955954bcb</t>
+          <t>0x412ca4afd615cfe359f5968bc40948ce23cddae9e71056cbb19853b8ae02c679</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -874,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>29.38999</t>
+          <t>0.00141</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Jupiler League</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV -1</t>
+          <t>Standard de Liege 0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -899,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x9328587a10f85b7926851709a75b7375b80be67ff4c9dbec51091d4e4551a6a5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786179429</t>
+          <t>1786204512</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>56.114539</t>
+          <t>0.002501</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,39 +979,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x00da5541f47274f81a987850455ebf6974f1794b7c0c6de63de3bf7812b4b198</t>
+          <t>0x9cc65e3f49b4912c50939d4b399a0688714223408f6802dbb3c9c508bf40bf32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>76.35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>R.Union Saint-Gilloise</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KVC Westerlo vs R.Union Saint-Gilloise</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R.Union Saint-Gilloise</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x446634efd727b2ef8bf251a191d1a7adf03939ea15fc66483ea568f8490e8d26</t>
+          <t>0x9e4dc3644ade05c02a5f24b797c1a14d4fbf75bc3f6c303b3d8feae8b0591871</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19453183</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786176782</t>
+          <t>1786204258</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>136.339286</t>
+          <t>9.876543</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x811eb7da21a4f297ed99b71c62d942341bcfb84e4030c6a1b2583e59d5b38248</t>
+          <t>0x65039eed52b65b480663aa7c404a69595947196ce60d1f3e8cfed8da14f02d77</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.51999</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV -1</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786176744</t>
+          <t>1786203912</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>56.362749</t>
+          <t>16.506329</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,27 +1195,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x9beed733469e724bd6c204e6d1758b8f78df08603ec5dcb7f1345f5b7855f05b</t>
+          <t>0xa88144d0f0678ca0ebd830fb868d23073c039c0834cd92c64128d12a99bebe9e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>107.95</t>
+          <t>47.16464</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6438</t>
+          <t>1.6162</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1223,11 +1219,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Saint-Truiden VV</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0e8a6aba98b8efbd7b13f11140ff85974fc8741094562833dce18f9958e3a56d</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786176743</t>
+          <t>1786203883</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>167.68932</t>
+          <t>76.534913</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,39 +1299,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x866b09603f0681c7636d7decb90bc14a623d02cda27a0e847225f18eeac82ace</t>
+          <t>0xfc6912e5274b4dd1a5142067e7c87269485f814956ebd8010536d8162aefb09c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>1.46965</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Saint-Truiden VV -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1347,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV vs Lommel United</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Saint-Truiden VV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19453181</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786176743</t>
+          <t>1786202938</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786214700</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>43.570406</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,28 +1403,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
+          <t>0x4f09607d5aacf85522ef20e37318675e17b247f841cfd0679db0d9fd4639f414</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.00993</t>
+          <t>214.33067</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.6763</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1451,27 +1435,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
+          <t>0xc450f2c8fa01c149bcf4ed07b3609bb8cde972269e7ee9251d5efb4f66f85e28</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1480,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786138046</t>
+          <t>1786202938</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.14928</t>
+          <t>316.939993</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,12 +1507,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
+          <t>0x9064c18924e18edfd882cd879a375ebd88f7b2112e70a3a82bbbc60e743a62f4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1538,22 +1522,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.0588</t>
+          <t>1.4038</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Saint-Truiden VV -1.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1563,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x3ce3b912da8d2cc09432e1645bc2d7009b793c4d5b487c5947c3b8daf824d2e8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1608,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786133616</t>
+          <t>1786201078</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>365.617021</t>
+          <t>45.151703</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1635,12 +1619,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
+          <t>0xbd061b258afff1ccccfcb425b21a7778b207e56a01cb149c147cffa96b6b5612</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1650,12 +1634,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>25.08</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1675,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4cbecc143c84bf2751d340df6548109fa017fae9ceb1c82b2fec61832fb5c57e</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1720,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786129775</t>
+          <t>1786198730</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>146.452555</t>
+          <t>14.222222</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1747,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
+          <t>0xb9cf0828046d92629747328f1340643ced9e7a6648fe05f4599f72482509bf6e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>269.96</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5688</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1779,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x4cbecc143c84bf2751d340df6548109fa017fae9ceb1c82b2fec61832fb5c57e</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1824,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786129260</t>
+          <t>1786198719</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>474.654945</t>
+          <t>14.222222</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1851,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
+          <t>0x613302ffee78855ab08fb9cc808b4faf9a40484f07d23ddcb3749c15417c0696</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.53431</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2312</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1883,27 +1883,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
+          <t>0x3ce3b912da8d2cc09432e1645bc2d7009b793c4d5b487c5947c3b8daf824d2e8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786128818</t>
+          <t>1786198017</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>106.094314</t>
+          <t>16.525</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,31 +1955,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
+          <t>0xe8ba70d47dc49702bd6988ac3ab9bc7477c92d2731f9f10a122beb28a46db7f4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>122.26618</t>
+          <t>19.22667</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -1987,27 +1995,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x3ce3b912da8d2cc09432e1645bc2d7009b793c4d5b487c5947c3b8daf824d2e8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2032,17 +2040,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786128755</t>
+          <t>1786197848</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>201.676173</t>
+          <t>48.066675</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2067,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
+          <t>0x48207d407aaec9eeb3ab89d1f0486692696d0387c4f9bb63d8f505c5939bd5e6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,22 +2082,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>0.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.125</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2099,27 +2107,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x9e4dc3644ade05c02a5f24b797c1a14d4fbf75bc3f6c303b3d8feae8b0591871</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2144,17 +2152,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786128752</t>
+          <t>1786194078</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>489.6</t>
+          <t>1.99003</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,31 +2179,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
+          <t>0x227265b7d255f8053a28ab822859433045ee7b788b9bde319da52309366633b6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x9E555D159D333EAE7346aE58D3d57dDE9680a9F7</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>222.324</t>
+          <t>143.84338</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7325</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-3)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2203,27 +2219,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
+          <t>0x9e4dc3644ade05c02a5f24b797c1a14d4fbf75bc3f6c303b3d8feae8b0591871</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2248,17 +2264,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786128730</t>
+          <t>1786194030</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>303.513993</t>
+          <t>286.255483</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2275,27 +2291,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
+          <t>0x98b046718238b1fcd44c4da6528214adbbf94cec7085be83998a597cd95b8e42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28.31998</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.4725</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2303,11 +2315,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2315,27 +2323,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Royal Antwerp FC vs Waasland-Beveren</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x2e62b0f92e344d08a9881b897546df0f5cec438d6ca14eb4a57ed9c49a70ab5a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457069</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2360,17 +2368,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786128484</t>
+          <t>1786185126</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786295700</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>34.536561</t>
+          <t>18.941799</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2387,31 +2395,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
+          <t>0xbf4973ce0a06b2d9d47e780f622a4b8196461d660d202ffe65bf9bc72f90bdf9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1.3538</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2419,27 +2435,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xd5800bf6a48bcd5b9e43eb6948ccabf7f9e554beb82e412a5fbb5da4ad572555</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2464,17 +2480,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786128396</t>
+          <t>1786184656</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1.941748</t>
+          <t>14.134276</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,12 +2507,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
+          <t>0x936a18fe1afdd087978f7d5e8f90ef2718bdecbfc78b8cdfa11764df4b942fd5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2506,22 +2522,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>14.77</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3013</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (4.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Over 4.5</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2531,27 +2547,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Standard de Liege vs Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Standard de Liege</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Cercle Brugge KSV</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
+          <t>0x2d1a4c7696876ac9f4015929bd3fae6dcbfa799713665648d7b954488f68629c</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453185</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2576,17 +2592,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786128227</t>
+          <t>1786181026</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786205700</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>49.029046</t>
+          <t>74.977346</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,7 +2619,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
+          <t>0x3682c29acf60c0dd6b7204b9540a6266714a3c2ac807800fcfbefee955954bcb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2611,23 +2627,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>134.05326</t>
+          <t>29.38999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Saint-Truiden VV -1</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2635,27 +2659,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,17 +2704,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786128166</t>
+          <t>1786179429</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>152.33325</t>
+          <t>56.114539</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,7 +2731,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
+          <t>0x00da5541f47274f81a987850455ebf6974f1794b7c0c6de63de3bf7812b4b198</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2715,23 +2739,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>76.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>R.Union Saint-Gilloise</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -2739,27 +2771,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>KVC Westerlo vs R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>R.Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x446634efd727b2ef8bf251a191d1a7adf03939ea15fc66483ea568f8490e8d26</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453183</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,17 +2816,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786128067</t>
+          <t>1786176782</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15.902041</t>
+          <t>136.339286</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2843,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
+          <t>0x811eb7da21a4f297ed99b71c62d942341bcfb84e4030c6a1b2583e59d5b38248</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,22 +2858,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>308.60024</t>
+          <t>29.51999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV -1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2851,27 +2883,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2896,17 +2928,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786128055</t>
+          <t>1786176744</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>379.81568</t>
+          <t>56.362749</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,12 +2955,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
+          <t>0x9beed733469e724bd6c204e6d1758b8f78df08603ec5dcb7f1345f5b7855f05b</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2938,12 +2970,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>79.10999</t>
+          <t>107.95</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6438</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2953,7 +2985,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2963,27 +2995,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x0e8a6aba98b8efbd7b13f11140ff85974fc8741094562833dce18f9958e3a56d</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3008,17 +3040,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786128051</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>97.366142</t>
+          <t>167.68932</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,12 +3067,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
+          <t>0x866b09603f0681c7636d7decb90bc14a623d02cda27a0e847225f18eeac82ace</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3050,22 +3082,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV -1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3075,27 +3107,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>Saint-Truiden VV vs Lommel United</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>Saint-Truiden VV</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf125c1fe812edb183b76c0e04e6b3ec7f112260e5e7a9f6def26c48fc6cde513</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19453181</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3120,17 +3152,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786128045</t>
+          <t>1786176743</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786214700</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>43.570406</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,39 +3179,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
+          <t>0x5ffd9d7beb5f5e3ef3b7fb92af578983f33bef4e010197e429b14531fa59df1a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>1.00993</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -3187,27 +3211,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x8b25f5e1930f008a84718904e95bbe5e9c034adad9cb9c797fefebdacef593a9</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3232,17 +3256,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786128044</t>
+          <t>1786138046</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>1.14928</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,12 +3283,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
+          <t>0x352d370c0697e7ed518b3a2268586f49cfd92989121641c37072d3c344e90aea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3274,39 +3298,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.0588</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3314,7 +3338,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3344,7 +3368,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786128042</t>
+          <t>1786133616</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3378,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>365.617021</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,12 +3395,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
+          <t>0x4a4e0cf953cb0e28a4fdc550b69a1c698875c408150a7178a6d13d5cec79260b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3386,12 +3410,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.99998</t>
+          <t>25.08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.1713</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3401,24 +3425,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3426,7 +3450,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3456,7 +3480,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786128041</t>
+          <t>1786129775</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3490,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>6.153822</t>
+          <t>146.452555</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,54 +3507,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
+          <t>0x8fd6425df195624731f52e90568724138bff4767e33fbd5c154147c812974f95</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.23999</t>
+          <t>269.96</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.5688</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3538,7 +3554,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3568,7 +3584,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786128039</t>
+          <t>1786129260</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3578,7 +3594,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3.98768</t>
+          <t>474.654945</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3595,7 +3611,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
+          <t>0xdf250f21c435ad7085d3d1caad0723a934b848e1812c1ce1bfaa574632a01d48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3603,46 +3619,38 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>24.53431</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.2312</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3650,7 +3658,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x7c359922df0f6108daf4f2f0c18655d64806c45fdeb60a375bc7d0cada88c4b2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3680,7 +3688,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786128018</t>
+          <t>1786128818</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3690,7 +3698,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>31.458462</t>
+          <t>106.094314</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,7 +3715,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
+          <t>0x5b54fe9b329a7433e078e120afc0394e564eb804f97a1e8b147f2d67261dc2b5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3715,46 +3723,38 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.28997</t>
+          <t>122.26618</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786128016</t>
+          <t>1786128755</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>58.20304</t>
+          <t>201.676173</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
+          <t>0x69eacdde7576cac529a3b8971eaecafe22a3e1fe00bddb69a8faf8e069e9b162</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>98.03998</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3849,24 +3849,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786128011</t>
+          <t>1786128752</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>120.664591</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3931,7 +3931,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
+          <t>0x4140a3778a8823bee85382f2ae1a028986215a82da7fc1571afc09889886a153</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3939,46 +3939,38 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>33.29998</t>
+          <t>222.324</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.7325</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+          <t>Asian Handicap (-3)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -3986,7 +3978,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xc587ad97d912bc1654e2a4a3d0d9ec14687947cfea0313e9b7045f51a12be083</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4016,7 +4008,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786128009</t>
+          <t>1786128730</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4026,7 +4018,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>40.984591</t>
+          <t>303.513993</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,7 +4035,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
+          <t>0xfe9ea4f51d4d307a4a0f3541746e980229fbf8b10c7a0624c43060de751cc7dc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4058,12 +4050,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1631.86998</t>
+          <t>28.31998</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4128,7 +4120,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786127865</t>
+          <t>1786128484</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4138,7 +4130,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>2008.45536</t>
+          <t>34.536561</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4155,7 +4147,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
+          <t>0xb43b7086d21db446d8fdefafb828fddea747af0e1d544531e999e1a3169576d0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4163,46 +4155,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>352.99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.8125</t>
+          <t>1.515</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -4210,7 +4194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4240,7 +4224,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786127791</t>
+          <t>1786128396</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4250,7 +4234,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>434.449231</t>
+          <t>1.941748</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4267,12 +4251,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
+          <t>0x6a6ce2b8cb6e3a9f90608928d6ea92bc239f2a74a3915edc5470e7fb840f4052</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4282,39 +4266,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2495.72998</t>
+          <t>14.77</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.3013</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -4322,7 +4306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xe5d8f93e710130cb7d8adf7b58684cc00cc4f693dcddb88c95aab10ff57ad795</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4352,7 +4336,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786127694</t>
+          <t>1786128227</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4362,7 +4346,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3076.400592</t>
+          <t>49.029046</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4379,7 +4363,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
+          <t>0xea8f12344a4daefd6a779d02449d83b8b60791904d91e1edbc0dfca60e31d5ad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4387,19 +4371,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>684.26</t>
+          <t>134.05326</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4407,26 +4387,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -4434,7 +4410,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4464,7 +4440,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786127681</t>
+          <t>1786128166</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4474,7 +4450,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>843.46379</t>
+          <t>152.33325</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4491,7 +4467,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
+          <t>0x37fcd190dd2ec0bc4687119143547274643fc6923882fef3c99bb289bc2c3924</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4499,46 +4475,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>133.37999</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -4546,7 +4514,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4576,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786127674</t>
+          <t>1786128067</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4586,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>164.412931</t>
+          <t>15.902041</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4603,12 +4571,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
+          <t>0x979138123696cbe3b5824b3e9f1d29fba8b1bbd277a76936984e53ef5d4deca6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4618,12 +4586,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>581.61996</t>
+          <t>308.60024</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4688,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786127673</t>
+          <t>1786128055</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4698,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>716.94294</t>
+          <t>379.81568</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4715,12 +4683,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
+          <t>0x8c5773174c706a8fb65002b458fbc52dfdf32c0edaabb696a2885fbee694bbe0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4730,22 +4698,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2.30963</t>
+          <t>79.10999</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4770,7 +4738,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4800,7 +4768,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786127672</t>
+          <t>1786128051</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4810,7 +4778,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>5.922128</t>
+          <t>97.366142</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4827,7 +4795,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
+          <t>0x4346622c7e4dc37074a97b0e44dce03ca6f9fec3a1f2484666c63a88699df592</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4842,12 +4810,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4912,7 +4880,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786127659</t>
+          <t>1786128045</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4922,7 +4890,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4939,7 +4907,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
+          <t>0xeed5ae9d81b8fde8de1a6a23d55b03ee5d1919a0ae6c8164eff522facf7f73d8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4954,12 +4922,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.99997</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5024,7 +4992,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786127658</t>
+          <t>1786128044</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5034,7 +5002,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>6.163291</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5051,12 +5019,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
+          <t>0xef43eb12fcfeb16c2e4474b2a274b04732f41503a8933e14f79942cdedd9cda5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5066,12 +5034,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>48.74996</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5136,7 +5104,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786127651</t>
+          <t>1786128042</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5146,7 +5114,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>60.092401</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5163,12 +5131,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
+          <t>0x94c4f27b3c288dd55fa935e8bbf4e7f26117b3241eca679e15b63883eed0fb99</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5178,12 +5146,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>344.26996</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8113</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5248,7 +5216,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786127649</t>
+          <t>1786128041</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5258,7 +5226,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>424.36975</t>
+          <t>6.153822</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5275,12 +5243,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
+          <t>0x563580844977480429d1f9218e69fc26ba2da9d8be31dba529d2bcb353945423</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5290,12 +5258,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4.99996</t>
+          <t>3.23999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5360,7 +5328,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786127314</t>
+          <t>1786128039</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5370,7 +5338,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>6.13492</t>
+          <t>3.98768</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5387,7 +5355,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
+          <t>0x84ddb5dbfe36e346706c1deeec9dbb29c8b0921f97229d1f4a3440fd33e10b37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5402,22 +5370,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5012</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5442,7 +5410,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5472,7 +5440,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786128018</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5482,7 +5450,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>72.917706</t>
+          <t>31.458462</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5499,7 +5467,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
+          <t>0xd3d09963cfaefe316a69f731302cad8057ceb7e9046bc863e3c7b77f10a98efe</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5514,7 +5482,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>55.59996</t>
+          <t>47.28997</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5584,7 +5552,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786127301</t>
+          <t>1786128016</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5594,7 +5562,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>68.43072</t>
+          <t>58.20304</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5611,7 +5579,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
+          <t>0xf6aafdd0a591bdce6bbc66c9be87c778f5a47d5ab4ab007c07ced0843beef55c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5626,22 +5594,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>98.03998</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4988</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5666,7 +5634,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5696,7 +5664,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786126541</t>
+          <t>1786128011</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5706,7 +5674,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>27.949875</t>
+          <t>120.664591</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5723,7 +5691,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
+          <t>0x9aa5bfd742ba44fc21c6410fea32d9fd5b8e0480c45477ccb03ea51f184117b0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5731,23 +5699,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15.30389</t>
+          <t>33.29998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4925</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5770,7 +5746,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5800,7 +5776,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786126463</t>
+          <t>1786128009</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5810,7 +5786,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>31.073888</t>
+          <t>40.984591</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5827,31 +5803,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
+          <t>0x36cb70eacfcd1d74229f89b5f0b280a29147c9b5274e5b517ce6d437b1861fa6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>17.9835</t>
+          <t>1631.86998</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.3575</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5874,7 +5858,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5904,7 +5888,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786127865</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5914,7 +5898,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>50.303497</t>
+          <t>2008.45536</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5931,31 +5915,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
+          <t>0x82bed396d4d964dbf37d8df9a9443414b813271601760387553c707ac66daecf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>17.37973</t>
+          <t>352.99</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -5978,7 +5970,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6008,7 +6000,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786126462</t>
+          <t>1786127791</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6018,7 +6010,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>28.259724</t>
+          <t>434.449231</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6035,31 +6027,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
+          <t>0x958b5a20906fdf0109d6e224e68bbb25ae2923741eaab63d79309287082c9c43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2495.72998</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786126324</t>
+          <t>1786127694</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>2.704684</t>
+          <t>3076.400592</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6139,7 +6139,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
+          <t>0xf5ad8a153a473e12648cced77553f51d8ddce5f1a61fa6ee54ac643aa4c0f247</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6147,23 +6147,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>684.26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5063</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6186,7 +6194,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6216,7 +6224,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786126323</t>
+          <t>1786127681</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6226,7 +6234,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>26.508642</t>
+          <t>843.46379</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6243,12 +6251,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
+          <t>0x90068b3300efd06b84e4cec215789660b457c50b5f94423a719b2de6107b364c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6258,12 +6266,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>133.37999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6273,7 +6281,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6283,27 +6291,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6328,17 +6336,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786126259</t>
+          <t>1786127674</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>20.477987</t>
+          <t>164.412931</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6355,23 +6363,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
+          <t>0x6b080567010fc0c303cb960499d404d538df911ed807160cd39d9812fbbe8245</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9.79</t>
+          <t>581.61996</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6379,7 +6391,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6387,27 +6403,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>RSC Anderlecht vs RAAL La Louviere</t>
+          <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>RAAL La Louviere</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19457072</t>
+          <t>L19453184</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6432,17 +6448,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786126255</t>
+          <t>1786127673</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786293000</t>
+          <t>1786128300</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>21.282609</t>
+          <t>716.94294</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6459,31 +6475,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
+          <t>0x4107cf78f5388a2f7123ec5c1ef7694f7e16eb11b04fa94c0f7ba3697c8a2f87</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>24.75</t>
+          <t>2.30963</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6506,7 +6530,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6536,7 +6560,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786126126</t>
+          <t>1786127672</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6546,7 +6570,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>40.408163</t>
+          <t>5.922128</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6563,7 +6587,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
+          <t>0x57e9d5b6c3dc9953ef1ffcb3e1f35b0876a037819555f2465701172e035bd5ee</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6571,23 +6595,31 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6610,7 +6642,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6640,7 +6672,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786125835</t>
+          <t>1786127659</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6650,7 +6682,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>10.230179</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6667,31 +6699,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
+          <t>0x717c45901ec842968e3dc03ec99f4a097b615c4b600ed7458e67473736f95bbf</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.24657</t>
+          <t>4.99997</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -6714,7 +6754,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6744,7 +6784,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786125800</t>
+          <t>1786127658</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6754,7 +6794,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>4.596563</t>
+          <t>6.163291</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6771,12 +6811,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
+          <t>0x3cdd2b1014d0e667caf3e869d548798331de4fc0c2bf40ff238e6a9108420e83</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6786,12 +6826,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>48.74996</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.0737</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6801,32 +6841,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6856,7 +6896,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786125572</t>
+          <t>1786127651</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6866,7 +6906,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>291.389831</t>
+          <t>60.092401</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6883,12 +6923,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
+          <t>0xd504e99511f02ec6f010aea364e4ace5741a6a869d3d29fb91fc8a98b42afb83</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6898,22 +6938,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>80.45</t>
+          <t>344.26996</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.8113</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -6938,7 +6978,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6968,7 +7008,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786124871</t>
+          <t>1786127649</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6978,7 +7018,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>153.971292</t>
+          <t>424.36975</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6995,12 +7035,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
+          <t>0xbbc9c8590157d6bd7a59b7b532767dd9350fa7af468b6e656382ce3b0469d25b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7010,22 +7050,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>99.99999</t>
+          <t>4.99996</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5225</t>
+          <t>1.815</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7050,7 +7090,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7080,7 +7120,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786124841</t>
+          <t>1786127314</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7090,7 +7130,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>191.387541</t>
+          <t>6.13492</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7107,12 +7147,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
+          <t>0xe7bb4a6c66a99e4d92dfaf26f37c393168dfeffe5b7c098fe0e12aa135a9ce37</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7122,47 +7162,47 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.5012</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>Club Brugge KV -2</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7192,7 +7232,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786123773</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7202,7 +7242,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>210.896552</t>
+          <t>72.917706</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7219,23 +7259,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
+          <t>0xd4309071a777af32f3a66ac7107aed4be3b2e9601a1732f7b08f549479af102e</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>64.92966</t>
+          <t>55.59996</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.8788</t>
+          <t>1.8125</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7243,7 +7287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7266,7 +7314,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7296,7 +7344,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786123019</t>
+          <t>1786127301</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7306,7 +7354,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>73.88866</t>
+          <t>68.43072</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7323,12 +7371,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
+          <t>0xccc41038dec3fc7c8fd48acfbb7695ab1aa3a35781f45f5766cfff4a5127d0f1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7338,22 +7386,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>14.21</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4988</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7378,7 +7426,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7408,7 +7456,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786126541</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7418,7 +7466,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>27.326923</t>
+          <t>27.949875</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7435,27 +7483,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
+          <t>0x9c363b1056de101aa27b7242ff5867636f22a97d0c2deb419877c603a86e35ed</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>53.28297</t>
+          <t>15.30389</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.4925</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7463,11 +7507,7 @@
           <t>Under/Over (3.5)</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7520,7 +7560,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786122377</t>
+          <t>1786126463</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7530,7 +7570,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>102.46725</t>
+          <t>31.073888</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7547,39 +7587,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
+          <t>0x37d27a0e6bd02cd23566f61c9a37bc3a6e5894a967d9102b4b2804880806ecfb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>17.9835</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3575</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2)</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7602,7 +7634,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7632,7 +7664,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786122212</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7642,7 +7674,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>50.303497</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7659,39 +7691,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
+          <t>0x19ea49067c2faad4203e1cd843c36770651f8c3180c021c6d921506eb1a5788f</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17.37973</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.1325</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7714,7 +7738,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7744,7 +7768,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786121396</t>
+          <t>1786126462</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7754,7 +7778,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>30.188679</t>
+          <t>28.259724</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7771,7 +7795,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
+          <t>0x8a369773fbc948aef2f0cb1990d08d1c8fb0b79b1a3c26ee9656be72f94fbf66</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7782,17 +7806,17 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>17.97999</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7818,7 +7842,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7848,7 +7872,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786120528</t>
+          <t>1786126324</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7858,7 +7882,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>20.54856</t>
+          <t>2.704684</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7875,7 +7899,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
+          <t>0xa2a47443555a1ed53da8269e05eee3e495ae06c9f491efe8f9856a506ae85cb9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7883,31 +7907,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5.21</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.5063</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -7930,7 +7946,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7960,7 +7976,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786120011</t>
+          <t>1786126323</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7970,7 +7986,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13.488673</t>
+          <t>26.508642</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7987,12 +8003,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
+          <t>0x8d35b043ba65f60b9850bb202cbedfc9df942ced9cbaa32c6acb5a7264bc8ddb</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8002,22 +8018,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Club Brugge KV -2.5</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8027,27 +8043,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0xdc61f3d380e6f20b29442628431126e2ce265ec2e5d7f46de3b5396c423a8738</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -8072,17 +8088,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786119466</t>
+          <t>1786126259</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>11.935275</t>
+          <t>20.477987</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8099,39 +8115,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
+          <t>0xd5256deda7c633df45cec5ddaedc6c54abc1c1be17c8d1eb50654d7781b1002c</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.3862</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (-2.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Club Brugge KV -2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8139,27 +8147,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
+          <t>RSC Anderlecht vs RAAL La Louviere</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RAAL La Louviere</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
+          <t>0x1b4e3c0070e4d18a4e184331914c54000d75ca6743954d57c514aa678cdb7ebf</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19453184</t>
+          <t>L19457072</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -8184,17 +8192,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786116893</t>
+          <t>1786126255</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1786128300</t>
+          <t>1786293000</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>18.330097</t>
+          <t>21.282609</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8211,39 +8219,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
+          <t>0x7344580e509c406b25c8451f291db61f6771d646f87bd36c6c2335870365f529</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>24.75</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-2.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8266,7 +8266,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786116378</t>
+          <t>1786126126</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>297.029703</t>
+          <t>40.408163</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8323,28 +8323,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
+          <t>0xf340d533069315cf4c54437c9b46efb6061fce2866f0e38f62f211bb9c6eb839</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>40.57051</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786115848</t>
+          <t>1786125835</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>135.235033</t>
+          <t>10.230179</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8427,28 +8427,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
+          <t>0x2a97cea480cc18e472bfb4baef1aab9dc38010c027920e78fff5886e1abd3174</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.24657</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786115833</t>
+          <t>1786125800</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>34.042553</t>
+          <t>4.596563</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8531,31 +8531,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
+          <t>0xc466c72a70738ab42d7a9ffae6d3f05ae255cad5ef76dd58f347ca0580e10fa8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21.49</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.2937</t>
+          <t>1.0737</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8578,7 +8586,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -8608,7 +8616,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786115818</t>
+          <t>1786125572</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8618,7 +8626,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>40.851064</t>
+          <t>291.389831</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8635,31 +8643,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
+          <t>0xd3d3f18154e3d1691d5319842abfcb9fe75cca7740c3b9cbd63dadbebfa1a696</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9.52632</t>
+          <t>80.45</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.2963</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8682,7 +8698,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8712,7 +8728,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786115807</t>
+          <t>1786124871</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8722,7 +8738,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>32.156354</t>
+          <t>153.971292</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8739,31 +8755,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
+          <t>0x8609728ccb3461cda00bea75b7c4db38df08645639d981e00f7c6dd5f4a01dac</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.7069</t>
+          <t>99.99999</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.5225</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8786,7 +8810,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8816,7 +8840,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786115795</t>
+          <t>1786124841</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8826,7 +8850,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>5.786102</t>
+          <t>191.387541</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8843,31 +8867,39 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
+          <t>0xc531d221691bf1a1d8aae07f342d851d32568603b9ec8130505614c7e404427f</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>12.16858</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -8890,7 +8922,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8920,7 +8952,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786115779</t>
+          <t>1786123773</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8930,7 +8962,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>41.249424</t>
+          <t>210.896552</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8947,28 +8979,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
+          <t>0xedf3b45b4032f401f047e315e5b862b85b0a84f7a75603ef59752b54b9996251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16.20886</t>
+          <t>64.92966</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.8788</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8994,7 +9026,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9024,7 +9056,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786115758</t>
+          <t>1786123019</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9034,7 +9066,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>54.945288</t>
+          <t>73.88866</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9051,7 +9083,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
+          <t>0xb9bede62c49f3ee0330e83f95e775dd7f4f8f578e731a9e38170c85261e46413</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9066,22 +9098,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9.54904</t>
+          <t>14.21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9106,7 +9138,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9136,7 +9168,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786115106</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9146,7 +9178,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>25.129053</t>
+          <t>27.326923</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9163,12 +9195,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
+          <t>0xb2d2766dfa30b480b378c0a171821d62791b76a59ce0a8659bb41a35f082e2cb</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -9178,39 +9210,39 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>116.54545</t>
+          <t>53.28297</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.8013</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -9218,7 +9250,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9248,7 +9280,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786112573</t>
+          <t>1786122377</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9258,7 +9290,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>145.45454</t>
+          <t>102.46725</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9275,12 +9307,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+          <t>0x443f15dbbcbde3579b5dd49ddf4fe28e945f7ffa5159aac86e8ee1c22bb45463</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -9290,22 +9322,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-2)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Club Brugge KV -2</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9330,7 +9362,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x397bd1d6187a0c9679021014076186b7a6b0e96fa781af1e338263507db90beb</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9360,7 +9392,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786111169</t>
+          <t>1786122212</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9370,7 +9402,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>28.755668</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9387,23 +9419,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+          <t>0x74fa3eabe74ec69a2e29a895f3dd76407ca4006c101d95434122f8d6d94230cc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0x403558C308Dbb56F024A307d85CAF3F3f061F8C3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>16.44995</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.8712</t>
+          <t>1.1325</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9411,7 +9447,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -9464,7 +9504,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786107764</t>
+          <t>1786121396</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9474,7 +9514,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>18.880861</t>
+          <t>30.188679</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9491,7 +9531,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+          <t>0x7d3f60b71d34bfa91d4f2fed0a9407ee8a9517e0cb3606116100171e789586af</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9502,12 +9542,12 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15.56556</t>
+          <t>17.97999</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.2087</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9538,7 +9578,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9568,7 +9608,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786106877</t>
+          <t>1786120528</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9578,7 +9618,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>74.565557</t>
+          <t>20.54856</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9595,7 +9635,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+          <t>0x07268a7aaed10e0b0dbd5bbea7ed629b1e7fee91beb7f09bc4e93752674c171f</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9610,39 +9650,39 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>5.21</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.7975</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -9650,7 +9690,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9680,7 +9720,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786102693</t>
+          <t>1786120011</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9690,7 +9730,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>49.37931</t>
+          <t>13.488673</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9707,7 +9747,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+          <t>0x7582d340c95cf1202eb1ce3f90a2e84500dea27e3784e636cc909426dca4796f</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9722,39 +9762,39 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>164.62998</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K86" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -9762,7 +9802,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9792,7 +9832,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786099074</t>
+          <t>1786119466</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9802,7 +9842,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>206.109521</t>
+          <t>11.935275</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9819,7 +9859,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+          <t>0x0dbfbfe99b2227e7cefe9f4de636c887eb71035fa36b26d305da508393b7f443</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9834,39 +9874,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>58.71998</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.3862</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-2.5)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>Club Brugge KV -2.5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K87" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -9874,7 +9914,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0xf330a5a82990b2d40308fa2f69ca0214f2f1aa3904d18266efb4e8c57f5549de</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9904,7 +9944,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786098454</t>
+          <t>1786116893</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9914,7 +9954,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>73.514842</t>
+          <t>18.330097</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9931,12 +9971,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+          <t>0x2291a76c9b99041f7d259ae4aacf121e9dffa4af25b03606af0a6e16a6fd8fdd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xa141274f45d09C2533035cd3c6ab42F3470dF7A8</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9946,39 +9986,39 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>80.26999</t>
+          <t>150</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.505</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K88" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -9986,7 +10026,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10016,7 +10056,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786116378</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10026,7 +10066,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>100.49451</t>
+          <t>297.029703</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10043,54 +10083,46 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+          <t>0xb7b0c0e45401ddac4cb27a6ae6909a41578aae821f07201cd53c89c00657d4ae</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>92.22997</t>
+          <t>40.57051</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
       <c r="K89" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
@@ -10098,7 +10130,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10128,7 +10160,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786098453</t>
+          <t>1786115848</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10138,7 +10170,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>115.467881</t>
+          <t>135.235033</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10155,28 +10187,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+          <t>0xdefe2f88334c5f294ac1b7affa40170a36f45ca2a30c903039307e942067f1de</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>16.47999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.6763</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -10202,7 +10234,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10232,7 +10264,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786084723</t>
+          <t>1786115833</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10242,7 +10274,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>24.369671</t>
+          <t>34.042553</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10259,28 +10291,28 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+          <t>0x271b94ec300382a3d301b51be1b84fb5bfd39cce50e81759482762c5ecd726ad</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.5513</t>
+          <t>1.2937</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -10306,7 +10338,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10336,7 +10368,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786079889</t>
+          <t>1786115818</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10346,7 +10378,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>30.802721</t>
+          <t>40.851064</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10363,23 +10395,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+          <t>0xe0f7343dd7cded685fd5aadeb7752a5bba953b172906612b9c34e4b199462f75</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>107.13792</t>
+          <t>9.52632</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.2963</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10440,7 +10472,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786078469</t>
+          <t>1786115807</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10450,7 +10482,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>330.927938</t>
+          <t>32.156354</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10467,28 +10499,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+          <t>0xe6c91a33c08ac1d40278bcc7bea4bae390ca64fa45491302cf9f7d2b246b3388</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.7069</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -10514,7 +10546,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10544,7 +10576,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786075639</t>
+          <t>1786115795</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10554,7 +10586,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2.531343</t>
+          <t>5.786102</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10571,62 +10603,54 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+          <t>0x566a263b8f66bd3e81b46067f2adfe199de95b5ef1646cc797bcef224d3af523</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>13.42578</t>
+          <t>12.16858</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.0762</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Jupiler League</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Club Brugge KV vs KV Kortrijk</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Club Brugge KV</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>KV Kortrijk</t>
-        </is>
-      </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10656,7 +10680,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786072637</t>
+          <t>1786115779</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10666,7 +10690,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>176.075803</t>
+          <t>41.249424</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10683,28 +10707,28 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+          <t>0x556bf851ea33ab6aa810045c66114ded73a0dc6d1ebbaf856535c655cc4bafd7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xca6360Efab0430fa8Dad766E9f6D20540B6c73ef</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2.06637</t>
+          <t>16.20886</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.1713</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -10730,7 +10754,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10760,7 +10784,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786068821</t>
+          <t>1786115758</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10770,7 +10794,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>12.066394</t>
+          <t>54.945288</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10787,7 +10811,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+          <t>0x903c7a3390ecf6ddd56f0fed3a331f31eaeff532c06bb784b75c7f4c98dffe48</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10795,23 +10819,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>9.54904</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.3237</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -10834,7 +10866,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10864,7 +10896,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786053446</t>
+          <t>1786115106</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10874,7 +10906,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>8.092664</t>
+          <t>25.129053</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10891,23 +10923,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+          <t>0x70f7f5f2db95efddebfb50309303238fa123ab7a098ea0d2aab0bed1f9fed4ae</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>0x40C6406af6250bDC2d12E0AA4053630789f332c2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>116.54545</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.2275</t>
+          <t>1.8013</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10915,7 +10951,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Jupiler League</t>
@@ -10968,7 +11008,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786047040</t>
+          <t>1786112573</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10978,7 +11018,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>79.78022</t>
+          <t>145.45454</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10995,110 +11035,1830 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>0xbf82c8bf64ba7e75f210f96d28a7f80622ca93df98f81c47837085f64fdc23f0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>14.27</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.4963</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786111169</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>28.755668</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0x326c4149609e5248e45fff82d77b1b6a3fafcc0cc1141389411822fc634c1c92</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>16.44995</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.8712</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786107764</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>18.880861</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0xf5ba73368aaf1bc2f319c9cafdbf725c20d31e713735b66af6a24917673d0bd4</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>15.56556</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.2087</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1786106877</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>74.565557</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x70363c9f57a945e6581303176de3a5739f1375b1ae340ca0ae3956cbc5eec70b</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>39.38</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.7975</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1786102693</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>49.37931</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x70bd650d25700f481c481a685823258abce132151922dc150de5b491ec0a8e8c</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>164.62998</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1786099074</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>206.109521</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0xa69553a89138d081401091ec63f550e626fc702d47adb208abf62f19161c50b9</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>58.71998</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1786098454</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>73.514842</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0xe504bdbf678d1dae7ed9a46872bec2230f2aee1479281f77beeeee9c690f6a97</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>80.26999</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>100.49451</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0x6bf410d1563fcce208c20d550a62f9b11147ac8f6017507706ea0111e12587c8</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>92.22997</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1786098453</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>115.467881</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0x4428af0b714cd02c16e716e5fffd60b12063db66560dd88f70adffeefe9baec4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>16.47999</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.6763</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0x4f30f712712bb3fbfe24564e4fb5237c8632863d61644010b41c81993d1aaa6b</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1786084723</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>24.369671</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0xd418b41e264209252b738215a66b7e78fa0ece08e8219f9b8515ad103a18bdf0</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.5513</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0x5573bcc31b50c3157311031c39bfbe1d0592d1b4be1a38efd61e40c6a3f4bf9f</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1786079889</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>30.802721</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0x84b8d4368856a6de1e1580a209235e1de14e1858745bd0951d1036613867076d</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>107.13792</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1786078469</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>330.927938</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>0x65a1f40efe4f8304309616a05f2e17e86b90ff4cbefcb1575b422e3f094db9fd</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0x6e3545220c021460178a753f72c94f3bdc39b25b1db7acc06332833c51b16a7b</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1786075639</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>2.531343</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0xb071fe2b7c2a6784a159d897713d1599b171af1f5b4788251884f6c410c86914</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>13.42578</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.0762</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0x24ef909dc756b058f4bd99d0a034a9e85c45eff2319a69f876fea7461334dea3</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1786072637</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>176.075803</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0x9df37bdd2a6c3b8b897002cd51096c135c9168d7b8947a1d6316f2f8dae3e828</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2.06637</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.1713</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>0xe2658f37be5ea92097979a1992f5c8cce5e7389795f21ff51094a41bf3c0231c</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>1786068821</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>12.066394</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0x8e5a34b35110bb5418a07b52d7e0f879e10398e7e68e1c0e54ba1d17927f58bc</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.3237</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>0x4937d8af628761601484db1ccd581e7d2dde4744b925fb09c660b5030bd65ec9</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>1786053446</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>8.092664</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0xae1c40433a387d3e160c3f482c36c347908d7b62a6d9acbef1b9a3417e77039c</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0x9B0B1AFA7bDED657DA5de911b1772ABe95e83290</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>18.15</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.2275</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Jupiler League</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Club Brugge KV vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Club Brugge KV</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>0xb7e709d4c259327ee20c2eac233626397889f1c291812b5ccb8dd8c68a28d3ba</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>L19453184</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>1786047040</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>1786128300</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>79.78022</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>0x17da446efa49f610050e7ecaeaec91964befc8f9d839eaf4eaf250bb1dc857a8</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>0.00029</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>Jupiler League</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>Club Brugge KV vs KV Kortrijk</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>Club Brugge KV</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>KV Kortrijk</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>0xd77ddb73d8a9ad095981816a0ffa614e557d5ed0af33c43936807c64f20a7c18</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>L19453184</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
         <is>
           <t>1786046726</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>1786128300</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T114" t="inlineStr">
         <is>
           <t>0.001933</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="U114" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="V114" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
